--- a/artfynd/A 10010-2025 artfynd.xlsx
+++ b/artfynd/A 10010-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123375419</v>
+        <v>123375488</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svallmyren, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>372581</v>
+        <v>372559</v>
       </c>
       <c r="R2" t="n">
-        <v>6941397</v>
+        <v>6941375</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123377686</v>
+        <v>123378047</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>56691</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +794,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Svallmyren, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372453</v>
+        <v>372379</v>
       </c>
       <c r="R3" t="n">
-        <v>6941109</v>
+        <v>6941156</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123378283</v>
+        <v>123378699</v>
       </c>
       <c r="B4" t="n">
-        <v>74863</v>
+        <v>77697</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6487</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372412</v>
+        <v>372343</v>
       </c>
       <c r="R4" t="n">
-        <v>6941193</v>
+        <v>6941183</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123378147</v>
+        <v>123374710</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>74866</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,42 +1007,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svallmyren, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372365</v>
+        <v>372806</v>
       </c>
       <c r="R5" t="n">
-        <v>6941201</v>
+        <v>6941375</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123375459</v>
+        <v>123377686</v>
       </c>
       <c r="B6" t="n">
-        <v>56688</v>
+        <v>78769</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,46 +1105,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Svallmyren, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372570</v>
+        <v>372453</v>
       </c>
       <c r="R6" t="n">
-        <v>6941390</v>
+        <v>6941109</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123375931</v>
+        <v>123375617</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>372620</v>
+        <v>372514</v>
       </c>
       <c r="R7" t="n">
-        <v>6941131</v>
+        <v>6941315</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123374554</v>
+        <v>123377878</v>
       </c>
       <c r="B8" t="n">
-        <v>74863</v>
+        <v>56691</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,41 +1309,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svallmyren, Hjd</t>
+          <t>Lemmorflon, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>372826</v>
+        <v>372439</v>
       </c>
       <c r="R8" t="n">
-        <v>6941360</v>
+        <v>6941040</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1399,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123375488</v>
+        <v>123374392</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,42 +1420,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Svallmyren, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>372559</v>
+        <v>372834</v>
       </c>
       <c r="R9" t="n">
-        <v>6941375</v>
+        <v>6941352</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>123378653</v>
       </c>
       <c r="B10" t="n">
-        <v>78150</v>
+        <v>78153</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123378699</v>
+        <v>123374925</v>
       </c>
       <c r="B11" t="n">
-        <v>77694</v>
+        <v>78769</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>372343</v>
+        <v>372758</v>
       </c>
       <c r="R11" t="n">
-        <v>6941183</v>
+        <v>6941457</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123377878</v>
+        <v>123378283</v>
       </c>
       <c r="B12" t="n">
-        <v>56688</v>
+        <v>74866</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1722,46 +1722,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lemmorflon, Hjd</t>
+          <t>Svallmyren, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>372439</v>
+        <v>372412</v>
       </c>
       <c r="R12" t="n">
-        <v>6941040</v>
+        <v>6941193</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1817,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123374392</v>
+        <v>123375419</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>372834</v>
+        <v>372581</v>
       </c>
       <c r="R13" t="n">
-        <v>6941352</v>
+        <v>6941397</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123374710</v>
+        <v>123378147</v>
       </c>
       <c r="B14" t="n">
-        <v>74863</v>
+        <v>57481</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1935,37 +1930,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Svallmyren, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>372806</v>
+        <v>372365</v>
       </c>
       <c r="R14" t="n">
-        <v>6941375</v>
+        <v>6941201</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2021,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123378047</v>
+        <v>123374554</v>
       </c>
       <c r="B15" t="n">
-        <v>56688</v>
+        <v>74866</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2033,46 +2033,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Svallmyren, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>372379</v>
+        <v>372826</v>
       </c>
       <c r="R15" t="n">
-        <v>6941156</v>
+        <v>6941360</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2128,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123374925</v>
+        <v>123375459</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>56691</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2140,41 +2135,46 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svallmyren, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>372758</v>
+        <v>372570</v>
       </c>
       <c r="R16" t="n">
-        <v>6941457</v>
+        <v>6941390</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2230,10 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123375617</v>
+        <v>123375931</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>372514</v>
+        <v>372620</v>
       </c>
       <c r="R17" t="n">
-        <v>6941315</v>
+        <v>6941131</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 10010-2025 artfynd.xlsx
+++ b/artfynd/A 10010-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123375488</v>
+        <v>123377878</v>
       </c>
       <c r="B2" t="n">
-        <v>57481</v>
+        <v>56691</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svallmyren, Hjd</t>
+          <t>Lemmorflon, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>372559</v>
+        <v>372439</v>
       </c>
       <c r="R2" t="n">
-        <v>6941375</v>
+        <v>6941040</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123378047</v>
+        <v>123374925</v>
       </c>
       <c r="B3" t="n">
-        <v>56691</v>
+        <v>78771</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,46 +794,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Svallmyren, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372379</v>
+        <v>372758</v>
       </c>
       <c r="R3" t="n">
-        <v>6941156</v>
+        <v>6941457</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,7 +887,7 @@
         <v>123378699</v>
       </c>
       <c r="B4" t="n">
-        <v>77697</v>
+        <v>77699</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123374710</v>
+        <v>123378047</v>
       </c>
       <c r="B5" t="n">
-        <v>74866</v>
+        <v>56691</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,41 +998,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svallmyren, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372806</v>
+        <v>372379</v>
       </c>
       <c r="R5" t="n">
-        <v>6941375</v>
+        <v>6941156</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123377686</v>
+        <v>123374554</v>
       </c>
       <c r="B6" t="n">
-        <v>78769</v>
+        <v>74866</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372453</v>
+        <v>372826</v>
       </c>
       <c r="R6" t="n">
-        <v>6941109</v>
+        <v>6941360</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123375617</v>
+        <v>123375419</v>
       </c>
       <c r="B7" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>372514</v>
+        <v>372581</v>
       </c>
       <c r="R7" t="n">
-        <v>6941315</v>
+        <v>6941397</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123377878</v>
+        <v>123374392</v>
       </c>
       <c r="B8" t="n">
-        <v>56691</v>
+        <v>78771</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,46 +1309,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lemmorflon, Hjd</t>
+          <t>Svallmyren, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>372439</v>
+        <v>372834</v>
       </c>
       <c r="R8" t="n">
-        <v>6941040</v>
+        <v>6941352</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1404,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123374392</v>
+        <v>123375617</v>
       </c>
       <c r="B9" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>372834</v>
+        <v>372514</v>
       </c>
       <c r="R9" t="n">
-        <v>6941352</v>
+        <v>6941315</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123378653</v>
+        <v>123375931</v>
       </c>
       <c r="B10" t="n">
-        <v>78153</v>
+        <v>78771</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>372343</v>
+        <v>372620</v>
       </c>
       <c r="R10" t="n">
-        <v>6941183</v>
+        <v>6941131</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123374925</v>
+        <v>123378147</v>
       </c>
       <c r="B11" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,37 +1619,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Svallmyren, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>372758</v>
+        <v>372365</v>
       </c>
       <c r="R11" t="n">
-        <v>6941457</v>
+        <v>6941201</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123378283</v>
+        <v>123374710</v>
       </c>
       <c r="B12" t="n">
         <v>74866</v>
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>372412</v>
+        <v>372806</v>
       </c>
       <c r="R12" t="n">
-        <v>6941193</v>
+        <v>6941375</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123375419</v>
+        <v>123377686</v>
       </c>
       <c r="B13" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>372581</v>
+        <v>372453</v>
       </c>
       <c r="R13" t="n">
-        <v>6941397</v>
+        <v>6941109</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123378147</v>
+        <v>123375459</v>
       </c>
       <c r="B14" t="n">
-        <v>57481</v>
+        <v>56691</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1926,25 +1926,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>372365</v>
+        <v>372570</v>
       </c>
       <c r="R14" t="n">
-        <v>6941201</v>
+        <v>6941390</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2021,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123374554</v>
+        <v>123378653</v>
       </c>
       <c r="B15" t="n">
-        <v>74866</v>
+        <v>78155</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2037,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>372826</v>
+        <v>372343</v>
       </c>
       <c r="R15" t="n">
-        <v>6941360</v>
+        <v>6941183</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2123,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123375459</v>
+        <v>123378283</v>
       </c>
       <c r="B16" t="n">
-        <v>56691</v>
+        <v>74866</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2135,46 +2135,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svallmyren, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>372570</v>
+        <v>372412</v>
       </c>
       <c r="R16" t="n">
-        <v>6941390</v>
+        <v>6941193</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2230,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123375931</v>
+        <v>123375488</v>
       </c>
       <c r="B17" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2246,37 +2241,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Svallmyren, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>372620</v>
+        <v>372559</v>
       </c>
       <c r="R17" t="n">
-        <v>6941131</v>
+        <v>6941375</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>

--- a/artfynd/A 10010-2025 artfynd.xlsx
+++ b/artfynd/A 10010-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123377878</v>
+        <v>123377686</v>
       </c>
       <c r="B2" t="n">
-        <v>56691</v>
+        <v>78772</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lemmorflon, Hjd</t>
+          <t>Svallmyren, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>372439</v>
+        <v>372453</v>
       </c>
       <c r="R2" t="n">
-        <v>6941040</v>
+        <v>6941109</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123374925</v>
+        <v>123378147</v>
       </c>
       <c r="B3" t="n">
-        <v>78771</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,37 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Svallmyren, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372758</v>
+        <v>372365</v>
       </c>
       <c r="R3" t="n">
-        <v>6941457</v>
+        <v>6941201</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123378699</v>
+        <v>123375488</v>
       </c>
       <c r="B4" t="n">
-        <v>77699</v>
+        <v>57481</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,37 +900,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6487</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Svallmyren, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372343</v>
+        <v>372559</v>
       </c>
       <c r="R4" t="n">
-        <v>6941183</v>
+        <v>6941375</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123378047</v>
+        <v>123374392</v>
       </c>
       <c r="B5" t="n">
-        <v>56691</v>
+        <v>78772</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,46 +1003,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svallmyren, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372379</v>
+        <v>372834</v>
       </c>
       <c r="R5" t="n">
-        <v>6941156</v>
+        <v>6941352</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123374554</v>
+        <v>123375419</v>
       </c>
       <c r="B6" t="n">
-        <v>74866</v>
+        <v>78772</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372826</v>
+        <v>372581</v>
       </c>
       <c r="R6" t="n">
-        <v>6941360</v>
+        <v>6941397</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123375419</v>
+        <v>123375459</v>
       </c>
       <c r="B7" t="n">
-        <v>78771</v>
+        <v>56691</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,41 +1207,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svallmyren, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>372581</v>
+        <v>372570</v>
       </c>
       <c r="R7" t="n">
-        <v>6941397</v>
+        <v>6941390</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1297,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123374392</v>
+        <v>123378653</v>
       </c>
       <c r="B8" t="n">
-        <v>78771</v>
+        <v>78156</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>372834</v>
+        <v>372343</v>
       </c>
       <c r="R8" t="n">
-        <v>6941352</v>
+        <v>6941183</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123375617</v>
+        <v>123377878</v>
       </c>
       <c r="B9" t="n">
-        <v>78771</v>
+        <v>56691</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,41 +1416,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svallmyren, Hjd</t>
+          <t>Lemmorflon, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>372514</v>
+        <v>372439</v>
       </c>
       <c r="R9" t="n">
-        <v>6941315</v>
+        <v>6941040</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1501,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123375931</v>
+        <v>123375617</v>
       </c>
       <c r="B10" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1541,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>372620</v>
+        <v>372514</v>
       </c>
       <c r="R10" t="n">
-        <v>6941131</v>
+        <v>6941315</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123378147</v>
+        <v>123374554</v>
       </c>
       <c r="B11" t="n">
-        <v>57481</v>
+        <v>74866</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,42 +1629,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Svallmyren, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>372365</v>
+        <v>372826</v>
       </c>
       <c r="R11" t="n">
-        <v>6941201</v>
+        <v>6941360</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1710,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123374710</v>
+        <v>123374925</v>
       </c>
       <c r="B12" t="n">
-        <v>74866</v>
+        <v>78772</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,21 +1731,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>372806</v>
+        <v>372758</v>
       </c>
       <c r="R12" t="n">
-        <v>6941375</v>
+        <v>6941457</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123377686</v>
+        <v>123378283</v>
       </c>
       <c r="B13" t="n">
-        <v>78771</v>
+        <v>74866</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1828,21 +1833,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>372453</v>
+        <v>372412</v>
       </c>
       <c r="R13" t="n">
-        <v>6941109</v>
+        <v>6941193</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123375459</v>
+        <v>123378699</v>
       </c>
       <c r="B14" t="n">
-        <v>56691</v>
+        <v>77700</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1926,46 +1931,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>6487</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Svallmyren, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>372570</v>
+        <v>372343</v>
       </c>
       <c r="R14" t="n">
-        <v>6941390</v>
+        <v>6941183</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2021,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123378653</v>
+        <v>123378047</v>
       </c>
       <c r="B15" t="n">
-        <v>78155</v>
+        <v>56691</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2033,41 +2033,46 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6437</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Svallmyren, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>372343</v>
+        <v>372379</v>
       </c>
       <c r="R15" t="n">
-        <v>6941183</v>
+        <v>6941156</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2123,7 +2128,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123378283</v>
+        <v>123374710</v>
       </c>
       <c r="B16" t="n">
         <v>74866</v>
@@ -2163,10 +2168,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>372412</v>
+        <v>372806</v>
       </c>
       <c r="R16" t="n">
-        <v>6941193</v>
+        <v>6941375</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2225,10 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123375488</v>
+        <v>123375931</v>
       </c>
       <c r="B17" t="n">
-        <v>57481</v>
+        <v>78772</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2241,42 +2246,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Svallmyren, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>372559</v>
+        <v>372620</v>
       </c>
       <c r="R17" t="n">
-        <v>6941375</v>
+        <v>6941131</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>

--- a/artfynd/A 10010-2025 artfynd.xlsx
+++ b/artfynd/A 10010-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123375459</v>
+        <v>123378699</v>
       </c>
       <c r="B2" t="n">
-        <v>56691</v>
+        <v>77709</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6487</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svallmyren, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>372570</v>
+        <v>372343</v>
       </c>
       <c r="R2" t="n">
-        <v>6941390</v>
+        <v>6941183</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123374710</v>
+        <v>123377878</v>
       </c>
       <c r="B3" t="n">
-        <v>74869</v>
+        <v>56697</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,41 +789,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svallmyren, Hjd</t>
+          <t>Lemmorflon, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372806</v>
+        <v>372439</v>
       </c>
       <c r="R3" t="n">
-        <v>6941375</v>
+        <v>6941040</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>123374925</v>
       </c>
       <c r="B4" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123378047</v>
+        <v>123374710</v>
       </c>
       <c r="B5" t="n">
-        <v>56691</v>
+        <v>74875</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,46 +998,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svallmyren, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372379</v>
+        <v>372806</v>
       </c>
       <c r="R5" t="n">
-        <v>6941156</v>
+        <v>6941375</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123375617</v>
+        <v>123375488</v>
       </c>
       <c r="B6" t="n">
-        <v>78775</v>
+        <v>57487</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,37 +1104,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Svallmyren, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372514</v>
+        <v>372559</v>
       </c>
       <c r="R6" t="n">
-        <v>6941315</v>
+        <v>6941375</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123375931</v>
+        <v>123378147</v>
       </c>
       <c r="B7" t="n">
-        <v>78775</v>
+        <v>57487</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,37 +1211,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svallmyren, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>372620</v>
+        <v>372365</v>
       </c>
       <c r="R7" t="n">
-        <v>6941131</v>
+        <v>6941201</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1300,7 +1305,7 @@
         <v>123377686</v>
       </c>
       <c r="B8" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1399,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123378147</v>
+        <v>123375419</v>
       </c>
       <c r="B9" t="n">
-        <v>57481</v>
+        <v>78781</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,42 +1420,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Svallmyren, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>372365</v>
+        <v>372581</v>
       </c>
       <c r="R9" t="n">
-        <v>6941201</v>
+        <v>6941397</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1506,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123377878</v>
+        <v>123378047</v>
       </c>
       <c r="B10" t="n">
-        <v>56691</v>
+        <v>56697</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1547,14 +1547,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lemmorflon, Hjd</t>
+          <t>Svallmyren, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>372439</v>
+        <v>372379</v>
       </c>
       <c r="R10" t="n">
-        <v>6941040</v>
+        <v>6941156</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1613,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123378699</v>
+        <v>123374554</v>
       </c>
       <c r="B11" t="n">
-        <v>77703</v>
+        <v>74875</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,21 +1629,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6487</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>372343</v>
+        <v>372826</v>
       </c>
       <c r="R11" t="n">
-        <v>6941183</v>
+        <v>6941360</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123374392</v>
+        <v>123378283</v>
       </c>
       <c r="B12" t="n">
-        <v>78775</v>
+        <v>74875</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,21 +1731,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>372834</v>
+        <v>372412</v>
       </c>
       <c r="R12" t="n">
-        <v>6941352</v>
+        <v>6941193</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123378283</v>
+        <v>123378653</v>
       </c>
       <c r="B13" t="n">
-        <v>74869</v>
+        <v>78165</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1833,21 +1833,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>372412</v>
+        <v>372343</v>
       </c>
       <c r="R13" t="n">
-        <v>6941193</v>
+        <v>6941183</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123375419</v>
+        <v>123374392</v>
       </c>
       <c r="B14" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>372581</v>
+        <v>372834</v>
       </c>
       <c r="R14" t="n">
-        <v>6941397</v>
+        <v>6941352</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2021,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123375488</v>
+        <v>123375617</v>
       </c>
       <c r="B15" t="n">
-        <v>57481</v>
+        <v>78781</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2037,42 +2037,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Svallmyren, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>372559</v>
+        <v>372514</v>
       </c>
       <c r="R15" t="n">
-        <v>6941375</v>
+        <v>6941315</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2128,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123378653</v>
+        <v>123375931</v>
       </c>
       <c r="B16" t="n">
-        <v>78159</v>
+        <v>78781</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2144,21 +2139,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2168,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>372343</v>
+        <v>372620</v>
       </c>
       <c r="R16" t="n">
-        <v>6941183</v>
+        <v>6941131</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2230,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123374554</v>
+        <v>123375459</v>
       </c>
       <c r="B17" t="n">
-        <v>74869</v>
+        <v>56697</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2242,41 +2237,46 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Svallmyren, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>372826</v>
+        <v>372570</v>
       </c>
       <c r="R17" t="n">
-        <v>6941360</v>
+        <v>6941390</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>

--- a/artfynd/A 10010-2025 artfynd.xlsx
+++ b/artfynd/A 10010-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123374710</v>
+        <v>123374372</v>
       </c>
       <c r="B2" t="n">
-        <v>74901</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>372806</v>
+        <v>372859</v>
       </c>
       <c r="R2" t="n">
-        <v>6941375</v>
+        <v>6941370</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,58 +772,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123377878</v>
+        <v>123374392</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lemmorflon, Hjd</t>
+          <t>Svallmyren, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372439</v>
+        <v>372834</v>
       </c>
       <c r="R3" t="n">
-        <v>6941040</v>
+        <v>6941352</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123378653</v>
+        <v>123374794</v>
       </c>
       <c r="B4" t="n">
-        <v>78194</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372343</v>
+        <v>372787</v>
       </c>
       <c r="R4" t="n">
-        <v>6941183</v>
+        <v>6941426</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,58 +966,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123375459</v>
+        <v>123374925</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Svallmyren, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372570</v>
+        <v>372758</v>
       </c>
       <c r="R5" t="n">
-        <v>6941390</v>
+        <v>6941457</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,58 +1063,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123375488</v>
+        <v>123375419</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Svallmyren, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372559</v>
+        <v>372581</v>
       </c>
       <c r="R6" t="n">
-        <v>6941375</v>
+        <v>6941397</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1200,19 +1160,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123375419</v>
+        <v>123375617</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1240,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>372581</v>
+        <v>372514</v>
       </c>
       <c r="R7" t="n">
-        <v>6941397</v>
+        <v>6941315</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,19 +1257,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123374925</v>
+        <v>123375931</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1342,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>372758</v>
+        <v>372620</v>
       </c>
       <c r="R8" t="n">
-        <v>6941457</v>
+        <v>6941131</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,16 +1357,11 @@
         <v>123377686</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1506,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123375931</v>
+        <v>123378653</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1522,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>372620</v>
+        <v>372343</v>
       </c>
       <c r="R10" t="n">
-        <v>6941131</v>
+        <v>6941183</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123378283</v>
+        <v>123374554</v>
       </c>
       <c r="B11" t="n">
-        <v>74901</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>372412</v>
+        <v>372826</v>
       </c>
       <c r="R11" t="n">
-        <v>6941193</v>
+        <v>6941360</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,58 +1645,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123378047</v>
+        <v>123374710</v>
       </c>
       <c r="B12" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Svallmyren, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>372379</v>
+        <v>372806</v>
       </c>
       <c r="R12" t="n">
-        <v>6941156</v>
+        <v>6941375</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1817,15 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123374392</v>
+        <v>123375987</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1833,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>372834</v>
+        <v>372630</v>
       </c>
       <c r="R13" t="n">
-        <v>6941352</v>
+        <v>6941120</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,15 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123375617</v>
+        <v>123378283</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>372514</v>
+        <v>372412</v>
       </c>
       <c r="R14" t="n">
-        <v>6941315</v>
+        <v>6941193</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2024,12 +1939,7 @@
         <v>123378699</v>
       </c>
       <c r="B15" t="n">
-        <v>77738</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2123,15 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123374554</v>
+        <v>123375488</v>
       </c>
       <c r="B16" t="n">
-        <v>74901</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2139,37 +2044,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svallmyren, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>372826</v>
+        <v>372559</v>
       </c>
       <c r="R16" t="n">
-        <v>6941360</v>
+        <v>6941375</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2228,12 +2138,7 @@
         <v>123378147</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2329,6 +2234,414 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>123375459</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Svallmyren, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>372570</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6941390</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>123377878</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lemmorflon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>372439</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6941040</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>123378047</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Svallmyren, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>372379</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6941156</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>123378782</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Svallmyren, Hjd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>372300</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6941173</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Tännäs</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10010-2025 artfynd.xlsx
+++ b/artfynd/A 10010-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123378653</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123378283</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123378699</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123378147</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123378047</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1269,6 +1299,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123378782</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1366,6 +1401,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123374372</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1463,6 +1503,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123374392</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1560,6 +1605,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123374794</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1657,6 +1707,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123374925</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1754,6 +1809,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123375419</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1851,6 +1911,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123375617</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1948,6 +2013,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123375931</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2045,6 +2115,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123377686</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2142,6 +2217,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123374554</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2239,6 +2319,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123374710</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2336,6 +2421,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123375987</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2438,6 +2528,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123375488</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2540,6 +2635,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123375459</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2642,8 +2742,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123377878</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>